--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:19:58+00:00</t>
+    <t>2026-06-29T12:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:41:53+00:00</t>
+    <t>2026-07-21T12:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,7 +513,7 @@
     <t>The overall type of event, intended for search and filtering purposes.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260619134042</t>
   </si>
   <si>
     <t>AdverseEvent.event</t>
@@ -657,7 +657,7 @@
     <t>Assessment whether this event was of real importance.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260619134042</t>
   </si>
   <si>
     <t>AdverseEvent.severity</t>
@@ -684,7 +684,7 @@
     <t>Describes the type of outcome from the adverse event.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260619134042</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>
@@ -818,7 +818,7 @@
     <t>Assessment of if the entity caused the event.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imputabilite-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imputabilite-cisis|20260619134042</t>
   </si>
   <si>
     <t>AdverseEvent.suspectEntity.causality.productRelatedness</t>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:27:37+00:00</t>
+    <t>2026-07-30T09:44:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>AdverseEvent.detected</t>
   </si>
   <si>
-    <t>Date de détection de l'effet indésirable</t>
+    <t>When the event was detected</t>
   </si>
   <si>
     <t>Estimated or actual date the AdverseEvent began, in the opinion of the reporter.</t>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>86</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>86</v>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="351">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:44:31+00:00</t>
+    <t>2026-07-30T14:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -420,33 +420,73 @@
     <t>AdverseEvent.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:code</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-AdverseEvent.code|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>Origine de l'effet indésirable (backport R5→R4)</t>
+  </si>
+  <si>
+    <t>Mime AdverseEvent.code (R5, renommage de AdverseEvent.event en R4) — non couvert par l'IG cross-version xver-r5.r4. Porte l'origine de l'effet indésirable (jdv-origine-effet-indesirable-cisis).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:outcome</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-AdverseEvent.outcome|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>Évolution de l'effet indésirable (backport R5→R4)</t>
+  </si>
+  <si>
+    <t>Mime AdverseEvent.outcome (R5, binding Example) — en R4 outcome a un binding Required qui interdit tout re-binding vers jdv-evolution-cisis. Non couvert par l'IG cross-version xver-r5.r4.</t>
+  </si>
+  <si>
+    <t>AdverseEvent.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>AdverseEvent.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -454,6 +494,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -507,13 +550,211 @@
 </t>
   </si>
   <si>
-    <t>Type d'effet indésirable</t>
+    <t>Type d'effet indésirable — fixé à medication-mishap (code R5)</t>
   </si>
   <si>
     <t>The overall type of event, intended for search and filtering purposes.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260619134042</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Overall categorization of the event, e.g. product-related or situational.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/adverse-event-category|4.0.1</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.id</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/adverse-event-category</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>medication-mishap</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>AdverseEvent.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>AdverseEvent.event</t>
@@ -678,13 +919,16 @@
     <t>AdverseEvent.outcome</t>
   </si>
   <si>
-    <t>Évolution de l'effet indésirable</t>
+    <t>resolved | recovering | ongoing | resolvedWithSequelae | fatal | unknown</t>
   </si>
   <si>
     <t>Describes the type of outcome from the adverse event.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis|20260619134042</t>
+    <t>TODO (and should this be required?).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome|4.0.1</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>
@@ -732,29 +976,7 @@
     <t>AdverseEvent.suspectEntity.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>AdverseEvent.suspectEntity.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>AdverseEvent.suspectEntity.modifierExtension</t>
@@ -1195,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL42"/>
+  <dimension ref="A1:AL55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="true" bestFit="true"/>
@@ -1223,10 +1445,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="57.65234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.94921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="46.7109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1234,7 +1456,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2114,11 +2336,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -2133,17 +2355,15 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>79</v>
@@ -2180,16 +2400,14 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -2210,7 +2428,7 @@
         <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -2218,43 +2436,41 @@
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>79</v>
       </c>
@@ -2302,7 +2518,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2311,7 +2527,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>137</v>
@@ -2320,17 +2536,19 @@
         <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>79</v>
       </c>
@@ -2348,23 +2566,19 @@
         <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O11" t="s" s="2">
         <v>148</v>
       </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -2412,19 +2626,19 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="AG11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -2442,14 +2656,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>79</v>
@@ -2458,19 +2672,23 @@
         <v>87</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -2494,13 +2712,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -2518,25 +2736,25 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>79</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2552,7 +2770,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>86</v>
@@ -2575,8 +2793,12 @@
       <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
@@ -2600,11 +2822,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -2628,7 +2852,7 @@
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>79</v>
@@ -2637,7 +2861,7 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>79</v>
@@ -2645,10 +2869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2656,7 +2880,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>86</v>
@@ -2665,19 +2889,19 @@
         <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2704,13 +2928,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -2728,10 +2952,10 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>86</v>
@@ -2743,7 +2967,7 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>79</v>
@@ -2751,14 +2975,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2785,12 +3009,8 @@
       <c r="M15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -2814,13 +3034,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -2838,13 +3058,13 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
@@ -2853,7 +3073,7 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>79</v>
@@ -2884,7 +3104,7 @@
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>177</v>
@@ -2895,9 +3115,7 @@
       <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -2946,7 +3164,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2958,13 +3176,13 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -2976,14 +3194,14 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -2992,18 +3210,20 @@
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3040,37 +3260,37 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
@@ -3089,7 +3309,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -3101,16 +3321,20 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
@@ -3158,13 +3382,13 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
@@ -3176,15 +3400,15 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>79</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3204,20 +3428,18 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3266,7 +3488,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3278,25 +3500,25 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3312,18 +3534,20 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3360,19 +3584,19 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3384,21 +3608,21 @@
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3421,16 +3645,20 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -3439,7 +3667,7 @@
         <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>79</v>
@@ -3478,7 +3706,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3496,15 +3724,15 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3512,7 +3740,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>86</v>
@@ -3527,15 +3755,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -3560,11 +3790,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -3582,7 +3814,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3600,15 +3832,15 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3631,16 +3863,18 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -3649,7 +3883,7 @@
         <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>79</v>
@@ -3664,13 +3898,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -3688,7 +3922,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3706,15 +3940,15 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3737,16 +3971,18 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -3770,11 +4006,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -3792,7 +4030,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3810,15 +4048,15 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>79</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3841,16 +4079,20 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -3898,7 +4140,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3913,18 +4155,18 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3935,7 +4177,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -3947,16 +4189,20 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4004,13 +4250,13 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
@@ -4022,15 +4268,15 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4038,10 +4284,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -4053,13 +4299,13 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4086,13 +4332,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4110,13 +4356,13 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
@@ -4125,7 +4371,7 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>79</v>
@@ -4133,18 +4379,18 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>86</v>
@@ -4156,19 +4402,23 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -4216,10 +4466,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>86</v>
@@ -4228,32 +4478,32 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -4262,19 +4512,19 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>132</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>133</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4324,69 +4574,65 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>132</v>
+        <v>261</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -4434,41 +4680,41 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>86</v>
@@ -4483,13 +4729,13 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4540,10 +4786,10 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>86</v>
@@ -4563,10 +4809,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4589,15 +4835,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -4646,13 +4894,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -4661,7 +4909,7 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -4669,10 +4917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4683,7 +4931,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -4692,16 +4940,16 @@
         <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4752,44 +5000,44 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -4798,20 +5046,18 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>132</v>
+        <v>278</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>133</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -4860,69 +5106,65 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -4946,13 +5188,11 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -4970,33 +5210,33 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5004,7 +5244,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>86</v>
@@ -5019,13 +5259,13 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5052,11 +5292,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5074,7 +5316,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5097,10 +5339,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5111,7 +5353,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -5123,13 +5365,13 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5156,13 +5398,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5180,7 +5422,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5203,10 +5445,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5229,13 +5471,13 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5286,7 +5528,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5301,7 +5543,7 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5309,10 +5551,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5323,7 +5565,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -5335,13 +5577,13 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>157</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5368,13 +5610,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -5392,13 +5634,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -5415,10 +5657,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5426,7 +5668,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>78</v>
@@ -5441,13 +5683,13 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5498,7 +5740,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5521,10 +5763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5535,7 +5777,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -5544,16 +5786,16 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>273</v>
+        <v>178</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>275</v>
+        <v>179</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5604,37 +5846,37 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>273</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5650,18 +5892,20 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -5710,7 +5954,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -5722,12 +5966,1398 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AK44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Y49" s="2"/>
+      <c r="Z49" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:18:46+00:00</t>
+    <t>2026-07-30T14:33:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:33:32+00:00</t>
+    <t>2026-07-30T14:45:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -464,6 +464,100 @@
 </t>
   </si>
   <si>
+    <t>AdverseEvent.extension:occurrence</t>
+  </si>
+  <si>
+    <t>occurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-AdverseEvent.occurrence|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Période de l'effet indésirable (backport R5 occurrence[x], Period)</t>
+  </si>
+  <si>
+    <t>R5: `AdverseEvent.occurrence[x]` additional types (Period, Timing)</t>
+  </si>
+  <si>
+    <t>Element `AdverseEvent.occurrence[x]` is mapped to FHIR R4 element `AdverseEvent.date` as `SourceIsBroaderThanTarget`.
+The mappings for `AdverseEvent.occurrence[x]` do not cover the following types: Period, Timing.</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:occurrence.id</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:occurrence.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:occurrence.url</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-AdverseEvent.occurrence</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:occurrence.value[x]</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>When the event occurred</t>
+  </si>
+  <si>
+    <t>The date (and perhaps time) when the adverse event occurred.</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
     <t>AdverseEvent.extension:outcome</t>
   </si>
   <si>
@@ -568,22 +662,6 @@
     <t>AdverseEvent.category.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>AdverseEvent.category.extension</t>
   </si>
   <si>
@@ -591,12 +669,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>AdverseEvent.category.coding</t>
@@ -831,9 +903,6 @@
   </si>
   <si>
     <t>Date de début de l'effet indésirable</t>
-  </si>
-  <si>
-    <t>The date (and perhaps time) when the adverse event occurred.</t>
   </si>
   <si>
     <t>FiveWs.init</t>
@@ -1417,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL55"/>
+  <dimension ref="A1:AL60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="true" bestFit="true"/>
@@ -2577,7 +2646,9 @@
       <c r="M11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
@@ -2649,46 +2720,42 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O12" t="s" s="2">
         <v>154</v>
       </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -2742,27 +2809,27 @@
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>129</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2773,7 +2840,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -2782,23 +2849,19 @@
         <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
@@ -2834,31 +2897,31 @@
         <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>79</v>
@@ -2869,7 +2932,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>162</v>
@@ -2889,13 +2952,13 @@
         <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>163</v>
@@ -2903,14 +2966,16 @@
       <c r="M14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N14" s="2"/>
+      <c r="N14" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>79</v>
@@ -2928,32 +2993,32 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>162</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>86</v>
       </c>
@@ -2964,18 +3029,18 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>79</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>169</v>
@@ -2986,7 +3051,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>86</v>
@@ -2998,7 +3063,7 @@
         <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>170</v>
@@ -3034,37 +3099,37 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>169</v>
-      </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
@@ -3073,20 +3138,22 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>79</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3107,13 +3174,13 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3164,37 +3231,37 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3207,7 +3274,7 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>79</v>
@@ -3216,15 +3283,17 @@
         <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3260,19 +3329,19 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3290,15 +3359,15 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>181</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3309,7 +3378,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -3321,19 +3390,19 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3382,13 +3451,13 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
@@ -3400,15 +3469,15 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3416,7 +3485,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>86</v>
@@ -3425,19 +3494,19 @@
         <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3464,13 +3533,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3488,10 +3557,10 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>86</v>
@@ -3500,32 +3569,32 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -3534,20 +3603,18 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3572,31 +3639,31 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3608,21 +3675,21 @@
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3642,23 +3709,19 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -3667,7 +3730,7 @@
         <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>79</v>
@@ -3706,7 +3769,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3718,32 +3781,32 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -3752,19 +3815,19 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3802,45 +3865,45 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>210</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3851,7 +3914,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -3863,7 +3926,7 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>212</v>
@@ -3871,9 +3934,11 @@
       <c r="M23" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -3883,7 +3948,7 @@
         <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>79</v>
@@ -3928,7 +3993,7 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
@@ -3968,21 +4033,19 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4030,7 +4093,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>155</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4042,32 +4105,32 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4076,23 +4139,21 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4128,45 +4189,45 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>231</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4189,19 +4250,19 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4211,7 +4272,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -4250,7 +4311,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4268,15 +4329,15 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4287,7 +4348,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -4299,15 +4360,17 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4332,13 +4395,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4356,7 +4419,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4371,26 +4434,26 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>86</v>
@@ -4405,19 +4468,17 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -4427,7 +4488,7 @@
         <v>79</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>79</v>
@@ -4466,10 +4527,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>86</v>
@@ -4481,18 +4542,18 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4515,18 +4576,18 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -4574,7 +4635,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4589,18 +4650,18 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4623,16 +4684,20 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -4680,7 +4745,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4695,18 +4760,18 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4729,16 +4794,20 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -4786,7 +4855,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4804,15 +4873,15 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4823,7 +4892,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -4835,17 +4904,15 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -4870,13 +4937,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -4894,7 +4961,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4909,7 +4976,7 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -4917,21 +4984,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -4943,16 +5010,20 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5000,13 +5071,13 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
@@ -5015,7 +5086,7 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -5057,7 +5128,9 @@
       <c r="M34" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5121,7 +5194,7 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
@@ -5129,10 +5202,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5140,7 +5213,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>86</v>
@@ -5155,13 +5228,13 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>172</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5188,11 +5261,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5210,7 +5285,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5225,7 +5300,7 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5233,10 +5308,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5259,13 +5334,13 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5292,13 +5367,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5316,7 +5391,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5353,7 +5428,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -5365,7 +5440,7 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>291</v>
@@ -5373,7 +5448,9 @@
       <c r="M37" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -5398,13 +5475,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5437,7 +5514,7 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5459,7 +5536,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -5534,7 +5611,7 @@
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
@@ -5543,7 +5620,7 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5551,10 +5628,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5565,7 +5642,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -5577,13 +5654,13 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5634,13 +5711,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -5657,10 +5734,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5671,7 +5748,7 @@
         <v>86</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -5683,13 +5760,13 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5716,13 +5793,11 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -5740,13 +5815,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -5763,10 +5838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5786,16 +5861,16 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>179</v>
+        <v>309</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5822,13 +5897,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -5846,7 +5921,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>180</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -5858,32 +5933,32 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -5892,20 +5967,18 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>183</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -5930,13 +6003,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -5954,69 +6027,65 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>318</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6064,44 +6133,44 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6113,13 +6182,13 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6170,13 +6239,13 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -6193,10 +6262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6204,10 +6273,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -6219,13 +6288,13 @@
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6276,7 +6345,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6299,10 +6368,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6325,13 +6394,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6382,7 +6451,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6400,19 +6469,19 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6434,13 +6503,13 @@
         <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6490,7 +6559,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6508,19 +6577,19 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6542,16 +6611,16 @@
         <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -6600,7 +6669,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6623,14 +6692,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6649,13 +6718,13 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>339</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6682,11 +6751,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -6704,10 +6775,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>86</v>
@@ -6727,10 +6798,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6753,13 +6824,13 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>177</v>
+        <v>327</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6810,13 +6881,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -6833,10 +6904,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6856,16 +6927,16 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>334</v>
+        <v>152</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>335</v>
+        <v>153</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>336</v>
+        <v>154</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6916,7 +6987,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>333</v>
+        <v>155</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -6928,32 +6999,32 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -6962,18 +7033,20 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>338</v>
+        <v>208</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -6998,13 +7071,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7022,37 +7095,37 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>160</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7065,22 +7138,26 @@
         <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>343</v>
+        <v>131</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -7128,7 +7205,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7140,21 +7217,21 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7162,10 +7239,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -7177,13 +7254,13 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>346</v>
+        <v>200</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7210,13 +7287,11 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -7234,13 +7309,13 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
@@ -7257,10 +7332,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7271,7 +7346,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -7283,13 +7358,13 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>349</v>
+        <v>152</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7340,13 +7415,13 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
@@ -7358,6 +7433,536 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:45:27+00:00</t>
+    <t>2026-07-30T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1072,7 +1072,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1)
+    <t xml:space="preserve">Reference(Immunization|4.0.1|Substance|4.0.1|Medication|4.0.1|MedicationAdministration|4.0.1|MedicationStatement|4.0.1)
 </t>
   </si>
   <si>
